--- a/frontend/public/test/test_applicants.xlsx
+++ b/frontend/public/test/test_applicants.xlsx
@@ -34,7 +34,7 @@
     <t>(주)알파테크놀로지</t>
   </si>
   <si>
-    <t>1234567890</t>
+    <t>1111111111</t>
   </si>
   <si>
     <t>경기도 수원시 영통구 광교로 156</t>
@@ -49,7 +49,7 @@
     <t>베타헬스케어</t>
   </si>
   <si>
-    <t>2345678902</t>
+    <t>2222222222</t>
   </si>
   <si>
     <t>경기도 성남시 분당구 판교로 289</t>
@@ -64,7 +64,7 @@
     <t>신규스타트업</t>
   </si>
   <si>
-    <t>9999999999</t>
+    <t>3333333333</t>
   </si>
   <si>
     <t>경기도 고양시 일산동구 중앙로 123</t>
@@ -76,7 +76,7 @@
     <t>감마정밀</t>
   </si>
   <si>
-    <t>3456789012</t>
+    <t>4444444444</t>
   </si>
   <si>
     <t>경기도 용인시 기흥구 흥덕중앙로 120</t>
@@ -91,7 +91,7 @@
     <t>에타파이낸스</t>
   </si>
   <si>
-    <t>7890123456</t>
+    <t>5555555555</t>
   </si>
   <si>
     <t>경기도 수원시 장안구 송원로 81</t>
